--- a/GenBOE/RDM.Web/Templates/Export/RatesImportExample.xlsx
+++ b/GenBOE/RDM.Web/Templates/Export/RatesImportExample.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="17668"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brunworg\Source\Workspaces\genBOE\dev\GenBOE\RDM.Web\Templates\Export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jueb\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{76D1EA1D-90C3-4341-8A47-33A34C988203}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="5190"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,8 +42,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -50,13 +51,71 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFECF0F1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFECF0F1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF452DB2"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF070729"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9F9F9F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF452DB2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD35714"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -68,14 +127,26 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="PPDuplicateRow" xfId="4" xr:uid="{808C3802-5321-4570-B532-A98CB71CC46D}"/>
+    <cellStyle name="PPHeaderColumn" xfId="2" xr:uid="{3B567352-437F-4BEE-A90E-C9CA170C3FEC}"/>
+    <cellStyle name="PPHeaderRequired" xfId="3" xr:uid="{79F8F166-D3E3-43BF-B9A1-E35ED41F8A41}"/>
+    <cellStyle name="PPHeaderTop" xfId="1" xr:uid="{053613E7-9E2A-4CA8-A037-4AFE77064200}"/>
+    <cellStyle name="PPInvalidValue" xfId="5" xr:uid="{E223972D-6DAB-4DD5-BC6F-F38C37575122}"/>
+    <cellStyle name="PPMissingValue" xfId="6" xr:uid="{47D8EFBD-0EEB-4000-AD77-B747A7B11C79}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -352,7 +423,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
